--- a/sheets/조재수대금교본/검수/야월삼경.xlsx
+++ b/sheets/조재수대금교본/검수/야월삼경.xlsx
@@ -3779,8 +3779,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ
-∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3792,8 +3791,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ
-∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3805,7 +3803,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3814,18 +3812,13 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3836,28 +3829,15 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="N4" s="24"/>
       <c r="O4" s="25"/>
-      <c r="P4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zㅎ</t>
-        </is>
-      </c>
+      <c r="P4" s="24"/>
       <c r="Q4" s="25"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -3897,11 +3877,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="21"/>
       <c r="M5" s="26"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="26"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="26"/>
@@ -3910,7 +3886,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
+          <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
@@ -3935,28 +3911,23 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧汰㳞
+          <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽
+          <t xml:space="preserve">淋
 湳</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-∧</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -3965,7 +3936,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
@@ -4006,7 +3977,7 @@
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋∽</t>
+淋</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -4022,7 +3993,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝∼
+          <t xml:space="preserve">南∼
 –南</t>
         </is>
       </c>
@@ -4030,7 +4001,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–汰∽</t>
+–汰</t>
         </is>
       </c>
       <c r="E8" s="26"/>
@@ -4043,8 +4014,7 @@
       <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧
-–湳</t>
+          <t xml:space="preserve">–湳</t>
         </is>
       </c>
       <c r="I8" s="26"/>
@@ -4055,11 +4025,7 @@
         </is>
       </c>
       <c r="K8" s="26"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="26"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
@@ -4092,14 +4058,14 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽太林
+          <t xml:space="preserve">太林
 –</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4136,7 +4102,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -4153,27 +4119,26 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -4184,15 +4149,11 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰∽</t>
+–汰</t>
         </is>
       </c>
       <c r="C11" s="26"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="26"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
@@ -4201,29 +4162,24 @@
         </is>
       </c>
       <c r="G11" s="26"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="26"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 –南</t>
         </is>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧
-湳</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝∼
+          <t xml:space="preserve">南∼
 –南</t>
         </is>
       </c>
@@ -4282,7 +4238,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽太林
+          <t xml:space="preserve">太林
 –∼</t>
         </is>
       </c>
@@ -4295,7 +4251,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4308,7 +4264,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -4320,8 +4276,7 @@
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4345,29 +4300,20 @@
       <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E14" s="26"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="26"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
@@ -4376,11 +4322,7 @@
         </is>
       </c>
       <c r="M14" s="26"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="26"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="26"/>

--- a/sheets/조재수대금교본/검수/야월삼경.xlsx
+++ b/sheets/조재수대금교본/검수/야월삼경.xlsx
@@ -3779,7 +3779,8 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ
+∽</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3791,7 +3792,8 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ
+∽</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3803,7 +3805,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3812,13 +3814,18 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3829,15 +3836,28 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="24"/>
+      <c r="N4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="25"/>
-      <c r="P4" s="24"/>
+      <c r="P4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="25"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -3886,7 +3906,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∧
 㳞</t>
         </is>
       </c>
@@ -3911,23 +3931,28 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">∧汰㳞
 –</t>
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
+          <t xml:space="preserve">淋∽
 湳</t>
         </is>
       </c>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳
+∧</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -3936,7 +3961,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 潢</t>
         </is>
       </c>
@@ -3977,7 +4002,7 @@
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋</t>
+淋∽</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -3993,7 +4018,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
+          <t xml:space="preserve">南⌝∼
 –南</t>
         </is>
       </c>
@@ -4001,7 +4026,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–汰</t>
+–汰∽</t>
         </is>
       </c>
       <c r="E8" s="26"/>
@@ -4014,7 +4039,8 @@
       <c r="G8" s="26"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–湳</t>
+          <t xml:space="preserve">∧
+–湳</t>
         </is>
       </c>
       <c r="I8" s="26"/>
@@ -4058,14 +4084,14 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太林
+          <t xml:space="preserve">∽太林
 –</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4102,7 +4128,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -4119,26 +4145,27 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 –潢</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 –潢</t>
         </is>
       </c>
@@ -4149,7 +4176,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-–汰</t>
+–汰∽</t>
         </is>
       </c>
       <c r="C11" s="26"/>
@@ -4166,20 +4193,21 @@
       <c r="I11" s="26"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 –南</t>
         </is>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">∧
+湳</t>
         </is>
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
+          <t xml:space="preserve">南⌝∼
 –南</t>
         </is>
       </c>
@@ -4238,7 +4266,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太林
+          <t xml:space="preserve">∽太林
 –∼</t>
         </is>
       </c>
@@ -4251,7 +4279,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋∼
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4264,7 +4292,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -4276,7 +4304,8 @@
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4309,7 +4338,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="I14" s="26"/>

--- a/sheets/조재수대금교본/검수/야월삼경.xlsx
+++ b/sheets/조재수대금교본/검수/야월삼경.xlsx
@@ -3713,28 +3713,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Q11" s="26"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4318,7 +4318,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4362,6 +4362,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
 </worksheet>
 </file>